--- a/src/main/resources/template/attendance.xlsx
+++ b/src/main/resources/template/attendance.xlsx
@@ -441,12 +441,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4726,7 +4726,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AH2" errorStyle="warning">
       <formula1>"1,2,3,4,5,6,7,8,9,10,11,12"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG26:AG29 C16:AG23 C24:AD27 C8:AG13 C28:AF29 C30:AG33 AE26:AF27 AE24:AG25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG26:AG29 C16:AG23 C24:AD27 C8:AG13 C28:AF29 C30:AG33 AE26:AF27 AE24:AG25 C14:AG15">
       <formula1>"/,起,事,病,T,婚,丧,□,★,休,年休,10,15,20,30,35,×,学,◆,△,会,修"</formula1>
     </dataValidation>
   </dataValidations>
